--- a/livros.xlsx
+++ b/livros.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Helmer\Documents\py\templates automação\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087FEE71-E85D-4710-9A35-EDA1EEFF81D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="735" windowWidth="19860" windowHeight="10050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="controle" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="623">
   <si>
     <t>livros</t>
   </si>
@@ -1889,16 +1883,13 @@
   </si>
   <si>
     <t>Sim</t>
-  </si>
-  <si>
-    <t>Líder interior</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1961,21 +1952,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2013,7 +1996,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2047,7 +2030,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2082,10 +2064,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2258,16 +2239,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C374"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="86" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2278,7 +2254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2289,7 +2265,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2300,7 +2276,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2311,7 +2287,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2322,7 +2298,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2333,7 +2309,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2344,7 +2320,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2355,7 +2331,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2366,7 +2342,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2377,7 +2353,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -2388,7 +2364,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -2399,7 +2375,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -2410,7 +2386,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -2421,7 +2397,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -2432,7 +2408,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2443,7 +2419,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2454,7 +2430,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2465,7 +2441,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2476,7 +2452,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2487,7 +2463,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2498,7 +2474,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2509,7 +2485,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2520,7 +2496,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2531,7 +2507,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2542,7 +2518,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -2553,7 +2529,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2564,7 +2540,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -2575,7 +2551,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2586,7 +2562,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -2597,7 +2573,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -2608,7 +2584,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -2619,7 +2595,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -2630,7 +2606,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -2641,7 +2617,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -2652,7 +2628,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -2663,7 +2639,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2674,7 +2650,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2685,7 +2661,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2696,7 +2672,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2707,7 +2683,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>31</v>
       </c>
@@ -2718,7 +2694,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2729,7 +2705,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -2740,7 +2716,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -2751,7 +2727,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2762,7 +2738,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -2773,7 +2749,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -2784,7 +2760,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -2795,7 +2771,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -2806,7 +2782,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -2817,7 +2793,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -2828,7 +2804,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -2839,7 +2815,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -2850,7 +2826,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -2861,7 +2837,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -2872,7 +2848,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -2883,7 +2859,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -2894,7 +2870,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -2905,7 +2881,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -2916,7 +2892,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -2927,7 +2903,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -2938,7 +2914,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -2949,7 +2925,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -2960,7 +2936,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -2971,7 +2947,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -2982,7 +2958,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -2993,7 +2969,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -3004,7 +2980,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -3015,7 +2991,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -3026,7 +3002,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -3037,7 +3013,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -3048,7 +3024,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -3059,7 +3035,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -3070,7 +3046,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -3081,7 +3057,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -3092,7 +3068,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -3103,39 +3079,51 @@
         <v>622</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>75</v>
       </c>
       <c r="B77" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>76</v>
       </c>
       <c r="B78" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>77</v>
       </c>
       <c r="B79" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
       <c r="B80" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>79</v>
       </c>
@@ -3146,55 +3134,73 @@
         <v>622</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>80</v>
       </c>
       <c r="B82" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>81</v>
       </c>
       <c r="B83" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>82</v>
       </c>
       <c r="B84" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
       <c r="B85" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>84</v>
       </c>
       <c r="B86" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C86" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>85</v>
       </c>
       <c r="B87" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>86</v>
       </c>
@@ -3205,95 +3211,128 @@
         <v>622</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>87</v>
       </c>
       <c r="B89" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>88</v>
       </c>
       <c r="B90" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C90" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>89</v>
       </c>
       <c r="B91" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>90</v>
       </c>
       <c r="B92" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>91</v>
       </c>
       <c r="B93" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>92</v>
       </c>
       <c r="B94" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>93</v>
       </c>
       <c r="B95" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>94</v>
       </c>
       <c r="B96" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>95</v>
       </c>
       <c r="B97" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C97" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>96</v>
       </c>
       <c r="B98" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C98" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>97</v>
       </c>
       <c r="B99" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C99" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>79</v>
       </c>
@@ -3304,31 +3343,37 @@
         <v>622</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>98</v>
       </c>
       <c r="B101" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C101" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>99</v>
       </c>
       <c r="B102" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C102" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>100</v>
       </c>
       <c r="C103" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>68</v>
       </c>
@@ -3339,7 +3384,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>101</v>
       </c>
@@ -3350,15 +3395,18 @@
         <v>622</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3">
       <c r="A106" t="s">
         <v>102</v>
       </c>
       <c r="B106" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>103</v>
       </c>
@@ -3369,7 +3417,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>39</v>
       </c>
@@ -3380,119 +3428,161 @@
         <v>622</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
         <v>104</v>
       </c>
       <c r="B109" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C109" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>105</v>
       </c>
       <c r="B110" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C110" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
         <v>106</v>
       </c>
       <c r="B111" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C111" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
       <c r="A112" t="s">
         <v>107</v>
       </c>
       <c r="B112" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C112" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>108</v>
       </c>
       <c r="B113" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C113" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
         <v>109</v>
       </c>
       <c r="B114" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C114" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115" t="s">
         <v>110</v>
       </c>
       <c r="B115" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C115" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
       <c r="A116" t="s">
         <v>111</v>
       </c>
       <c r="B116" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C116" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117" t="s">
         <v>112</v>
       </c>
       <c r="B117" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C117" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118" t="s">
         <v>113</v>
       </c>
       <c r="B118" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C118" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
         <v>114</v>
       </c>
       <c r="B119" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C119" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
       <c r="A120" t="s">
         <v>115</v>
       </c>
       <c r="B120" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C120" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
       <c r="A121" t="s">
         <v>116</v>
       </c>
       <c r="B121" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C121" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
       <c r="A122" t="s">
         <v>117</v>
       </c>
       <c r="B122" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C122" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
       <c r="A123" t="s">
         <v>118</v>
       </c>
@@ -3500,7 +3590,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3">
       <c r="A124" t="s">
         <v>119</v>
       </c>
@@ -3508,7 +3598,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3">
       <c r="A125" t="s">
         <v>120</v>
       </c>
@@ -3516,7 +3606,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
         <v>121</v>
       </c>
@@ -3524,7 +3614,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3">
       <c r="A127" t="s">
         <v>122</v>
       </c>
@@ -3532,7 +3622,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3">
       <c r="A128" t="s">
         <v>123</v>
       </c>
@@ -3540,7 +3630,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
         <v>124</v>
       </c>
@@ -3548,7 +3638,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>125</v>
       </c>
@@ -3556,15 +3646,18 @@
         <v>448</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
         <v>97</v>
       </c>
       <c r="B131" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C131" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
         <v>126</v>
       </c>
@@ -3572,7 +3665,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3">
       <c r="A133" t="s">
         <v>127</v>
       </c>
@@ -3580,7 +3673,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
         <v>128</v>
       </c>
@@ -3588,7 +3681,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3">
       <c r="A135" t="s">
         <v>129</v>
       </c>
@@ -3596,7 +3689,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3">
       <c r="A136" t="s">
         <v>130</v>
       </c>
@@ -3604,7 +3697,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3">
       <c r="A137" t="s">
         <v>131</v>
       </c>
@@ -3612,7 +3705,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3">
       <c r="A138" t="s">
         <v>132</v>
       </c>
@@ -3620,7 +3713,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3">
       <c r="A139" t="s">
         <v>133</v>
       </c>
@@ -3628,7 +3721,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3">
       <c r="A140" t="s">
         <v>134</v>
       </c>
@@ -3636,7 +3729,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3">
       <c r="A141" t="s">
         <v>135</v>
       </c>
@@ -3644,7 +3737,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3">
       <c r="A142" t="s">
         <v>136</v>
       </c>
@@ -3652,7 +3745,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3">
       <c r="A143" t="s">
         <v>137</v>
       </c>
@@ -3663,7 +3756,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3">
       <c r="A144" t="s">
         <v>138</v>
       </c>
@@ -3671,7 +3764,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
         <v>139</v>
       </c>
@@ -3679,7 +3772,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3">
       <c r="A146" t="s">
         <v>140</v>
       </c>
@@ -3687,7 +3780,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3">
       <c r="A147" t="s">
         <v>141</v>
       </c>
@@ -3695,7 +3788,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3">
       <c r="A148" t="s">
         <v>142</v>
       </c>
@@ -3703,7 +3796,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3">
       <c r="A149" t="s">
         <v>143</v>
       </c>
@@ -3714,12 +3807,12 @@
         <v>622</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3">
       <c r="A150" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3">
       <c r="A151" t="s">
         <v>145</v>
       </c>
@@ -3727,7 +3820,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3">
       <c r="A152" t="s">
         <v>146</v>
       </c>
@@ -3735,7 +3828,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3">
       <c r="A153" t="s">
         <v>147</v>
       </c>
@@ -3743,7 +3836,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3">
       <c r="A154" t="s">
         <v>148</v>
       </c>
@@ -3751,7 +3844,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3">
       <c r="A155" t="s">
         <v>149</v>
       </c>
@@ -3759,7 +3852,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3">
       <c r="A156" t="s">
         <v>150</v>
       </c>
@@ -3767,7 +3860,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3">
       <c r="A157" t="s">
         <v>151</v>
       </c>
@@ -3775,7 +3868,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3">
       <c r="A158" t="s">
         <v>152</v>
       </c>
@@ -3786,7 +3879,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3">
       <c r="A159" t="s">
         <v>153</v>
       </c>
@@ -3794,7 +3887,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3">
       <c r="A160" t="s">
         <v>154</v>
       </c>
@@ -3802,12 +3895,12 @@
         <v>475</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3">
       <c r="A161" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3">
       <c r="A162" t="s">
         <v>156</v>
       </c>
@@ -3815,7 +3908,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3">
       <c r="A163" t="s">
         <v>157</v>
       </c>
@@ -3823,17 +3916,17 @@
         <v>477</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3">
       <c r="A164" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3">
       <c r="A165" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3">
       <c r="A166" t="s">
         <v>160</v>
       </c>
@@ -3841,7 +3934,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3">
       <c r="A167" t="s">
         <v>161</v>
       </c>
@@ -3849,7 +3942,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3">
       <c r="A168" t="s">
         <v>162</v>
       </c>
@@ -3857,7 +3950,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3">
       <c r="A169" t="s">
         <v>163</v>
       </c>
@@ -3865,7 +3958,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3">
       <c r="A170" t="s">
         <v>164</v>
       </c>
@@ -3873,7 +3966,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3">
       <c r="A171" t="s">
         <v>165</v>
       </c>
@@ -3881,7 +3974,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3">
       <c r="A172" t="s">
         <v>166</v>
       </c>
@@ -3889,7 +3982,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3">
       <c r="A173" t="s">
         <v>167</v>
       </c>
@@ -3897,12 +3990,12 @@
         <v>483</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3">
       <c r="A174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3">
       <c r="A175" t="s">
         <v>169</v>
       </c>
@@ -3910,7 +4003,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3">
       <c r="A176" t="s">
         <v>170</v>
       </c>
@@ -3918,7 +4011,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2">
       <c r="A177" t="s">
         <v>171</v>
       </c>
@@ -3926,7 +4019,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2">
       <c r="A178" t="s">
         <v>172</v>
       </c>
@@ -3934,7 +4027,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2">
       <c r="A179" t="s">
         <v>173</v>
       </c>
@@ -3942,7 +4035,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2">
       <c r="A180" t="s">
         <v>145</v>
       </c>
@@ -3950,7 +4043,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2">
       <c r="A181" t="s">
         <v>174</v>
       </c>
@@ -3958,7 +4051,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
         <v>175</v>
       </c>
@@ -3966,7 +4059,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
         <v>176</v>
       </c>
@@ -3974,7 +4067,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2">
       <c r="A184" t="s">
         <v>177</v>
       </c>
@@ -3982,7 +4075,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
         <v>178</v>
       </c>
@@ -3990,7 +4083,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2">
       <c r="A186" t="s">
         <v>179</v>
       </c>
@@ -3998,7 +4091,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2">
       <c r="A187" t="s">
         <v>180</v>
       </c>
@@ -4006,7 +4099,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2">
       <c r="A188" t="s">
         <v>181</v>
       </c>
@@ -4014,7 +4107,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2">
       <c r="A189" t="s">
         <v>182</v>
       </c>
@@ -4022,7 +4115,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2">
       <c r="A190" t="s">
         <v>183</v>
       </c>
@@ -4030,7 +4123,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2">
       <c r="A191" t="s">
         <v>184</v>
       </c>
@@ -4038,7 +4131,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2">
       <c r="A192" t="s">
         <v>185</v>
       </c>
@@ -4046,7 +4139,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3">
       <c r="A193" t="s">
         <v>186</v>
       </c>
@@ -4054,7 +4147,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3">
       <c r="A194" t="s">
         <v>187</v>
       </c>
@@ -4062,7 +4155,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3">
       <c r="A195" t="s">
         <v>188</v>
       </c>
@@ -4070,7 +4163,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3">
       <c r="A196" t="s">
         <v>189</v>
       </c>
@@ -4078,7 +4171,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3">
       <c r="A197" t="s">
         <v>190</v>
       </c>
@@ -4086,7 +4179,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3">
       <c r="A198" t="s">
         <v>191</v>
       </c>
@@ -4094,7 +4187,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3">
       <c r="A199" t="s">
         <v>192</v>
       </c>
@@ -4102,7 +4195,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3">
       <c r="A200" t="s">
         <v>193</v>
       </c>
@@ -4110,7 +4203,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3">
       <c r="A201" t="s">
         <v>194</v>
       </c>
@@ -4118,7 +4211,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3">
       <c r="A202" t="s">
         <v>195</v>
       </c>
@@ -4126,7 +4219,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3">
       <c r="A203" t="s">
         <v>196</v>
       </c>
@@ -4137,7 +4230,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3">
       <c r="A204" t="s">
         <v>197</v>
       </c>
@@ -4145,7 +4238,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3">
       <c r="A205" t="s">
         <v>198</v>
       </c>
@@ -4153,7 +4246,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3">
       <c r="A206" t="s">
         <v>199</v>
       </c>
@@ -4161,7 +4254,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3">
       <c r="A207" t="s">
         <v>200</v>
       </c>
@@ -4169,7 +4262,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3">
       <c r="A208" t="s">
         <v>201</v>
       </c>
@@ -4177,7 +4270,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2">
       <c r="A209" t="s">
         <v>202</v>
       </c>
@@ -4185,7 +4278,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2">
       <c r="A210" t="s">
         <v>203</v>
       </c>
@@ -4193,7 +4286,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2">
       <c r="A211" t="s">
         <v>204</v>
       </c>
@@ -4201,7 +4294,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2">
       <c r="A212" t="s">
         <v>205</v>
       </c>
@@ -4209,7 +4302,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2">
       <c r="A213" t="s">
         <v>206</v>
       </c>
@@ -4217,7 +4310,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2">
       <c r="A214" t="s">
         <v>207</v>
       </c>
@@ -4225,7 +4318,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2">
       <c r="A215" t="s">
         <v>208</v>
       </c>
@@ -4233,7 +4326,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2">
       <c r="A216" t="s">
         <v>209</v>
       </c>
@@ -4241,7 +4334,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2">
       <c r="A217" t="s">
         <v>210</v>
       </c>
@@ -4249,7 +4342,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2">
       <c r="A218" t="s">
         <v>211</v>
       </c>
@@ -4257,7 +4350,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2">
       <c r="A219" t="s">
         <v>212</v>
       </c>
@@ -4265,7 +4358,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2">
       <c r="A220" t="s">
         <v>213</v>
       </c>
@@ -4273,7 +4366,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2">
       <c r="A221" t="s">
         <v>214</v>
       </c>
@@ -4281,7 +4374,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2">
       <c r="A222" t="s">
         <v>215</v>
       </c>
@@ -4289,7 +4382,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2">
       <c r="A223" t="s">
         <v>216</v>
       </c>
@@ -4297,7 +4390,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2">
       <c r="A224" t="s">
         <v>217</v>
       </c>
@@ -4305,7 +4398,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3">
       <c r="A225" t="s">
         <v>218</v>
       </c>
@@ -4313,7 +4406,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3">
       <c r="A226" t="s">
         <v>219</v>
       </c>
@@ -4321,7 +4414,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3">
       <c r="A227" t="s">
         <v>220</v>
       </c>
@@ -4329,7 +4422,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3">
       <c r="A228" t="s">
         <v>221</v>
       </c>
@@ -4337,7 +4430,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3">
       <c r="A229" t="s">
         <v>222</v>
       </c>
@@ -4345,7 +4438,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3">
       <c r="A230" t="s">
         <v>223</v>
       </c>
@@ -4353,7 +4446,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3">
       <c r="A231" t="s">
         <v>224</v>
       </c>
@@ -4361,7 +4454,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3">
       <c r="A232" t="s">
         <v>225</v>
       </c>
@@ -4369,7 +4462,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3">
       <c r="A233" t="s">
         <v>226</v>
       </c>
@@ -4377,7 +4470,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3">
       <c r="A234" t="s">
         <v>227</v>
       </c>
@@ -4385,7 +4478,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3">
       <c r="A235" t="s">
         <v>228</v>
       </c>
@@ -4393,7 +4486,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3">
       <c r="A236" t="s">
         <v>229</v>
       </c>
@@ -4401,7 +4494,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3">
       <c r="A237" t="s">
         <v>230</v>
       </c>
@@ -4409,7 +4502,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3">
       <c r="A238" t="s">
         <v>231</v>
       </c>
@@ -4417,7 +4510,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3">
       <c r="A239" t="s">
         <v>232</v>
       </c>
@@ -4428,7 +4521,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3">
       <c r="A240" t="s">
         <v>233</v>
       </c>
@@ -4436,7 +4529,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2">
       <c r="A241" t="s">
         <v>234</v>
       </c>
@@ -4444,7 +4537,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2">
       <c r="A242" t="s">
         <v>235</v>
       </c>
@@ -4452,7 +4545,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2">
       <c r="A243" t="s">
         <v>236</v>
       </c>
@@ -4460,7 +4553,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2">
       <c r="A244" t="s">
         <v>237</v>
       </c>
@@ -4468,7 +4561,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2">
       <c r="A245" t="s">
         <v>238</v>
       </c>
@@ -4476,7 +4569,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2">
       <c r="A246" t="s">
         <v>239</v>
       </c>
@@ -4484,7 +4577,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2">
       <c r="A247" t="s">
         <v>240</v>
       </c>
@@ -4492,7 +4585,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2">
       <c r="A248" t="s">
         <v>241</v>
       </c>
@@ -4500,7 +4593,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2">
       <c r="A249" t="s">
         <v>242</v>
       </c>
@@ -4508,7 +4601,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2">
       <c r="A250" t="s">
         <v>243</v>
       </c>
@@ -4516,7 +4609,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2">
       <c r="A251" t="s">
         <v>244</v>
       </c>
@@ -4524,7 +4617,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2">
       <c r="A252" t="s">
         <v>245</v>
       </c>
@@ -4532,7 +4625,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2">
       <c r="A253" t="s">
         <v>245</v>
       </c>
@@ -4540,7 +4633,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2">
       <c r="A254" t="s">
         <v>245</v>
       </c>
@@ -4548,7 +4641,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2">
       <c r="A255" t="s">
         <v>245</v>
       </c>
@@ -4556,7 +4649,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2">
       <c r="A256" t="s">
         <v>245</v>
       </c>
@@ -4564,7 +4657,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3">
       <c r="A257" t="s">
         <v>245</v>
       </c>
@@ -4572,7 +4665,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3">
       <c r="A258" t="s">
         <v>245</v>
       </c>
@@ -4580,7 +4673,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3">
       <c r="A259" t="s">
         <v>246</v>
       </c>
@@ -4591,7 +4684,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3">
       <c r="A260" t="s">
         <v>246</v>
       </c>
@@ -4602,7 +4695,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3">
       <c r="A261" t="s">
         <v>246</v>
       </c>
@@ -4613,7 +4706,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3">
       <c r="A262" t="s">
         <v>246</v>
       </c>
@@ -4624,7 +4717,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3">
       <c r="A263" t="s">
         <v>246</v>
       </c>
@@ -4635,7 +4728,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3">
       <c r="A264" t="s">
         <v>247</v>
       </c>
@@ -4646,7 +4739,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3">
       <c r="A265" t="s">
         <v>248</v>
       </c>
@@ -4654,7 +4747,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3">
       <c r="A266" t="s">
         <v>249</v>
       </c>
@@ -4662,7 +4755,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3">
       <c r="A267" t="s">
         <v>250</v>
       </c>
@@ -4670,7 +4763,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3">
       <c r="A268" t="s">
         <v>251</v>
       </c>
@@ -4678,7 +4771,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3">
       <c r="A269" t="s">
         <v>252</v>
       </c>
@@ -4686,7 +4779,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3">
       <c r="A270" t="s">
         <v>253</v>
       </c>
@@ -4694,7 +4787,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3">
       <c r="A271" t="s">
         <v>254</v>
       </c>
@@ -4702,7 +4795,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3">
       <c r="A272" t="s">
         <v>255</v>
       </c>
@@ -4710,7 +4803,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2">
       <c r="A273" t="s">
         <v>256</v>
       </c>
@@ -4718,7 +4811,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2">
       <c r="A274" t="s">
         <v>257</v>
       </c>
@@ -4726,7 +4819,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2">
       <c r="A275" t="s">
         <v>258</v>
       </c>
@@ -4734,7 +4827,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2">
       <c r="A276" t="s">
         <v>259</v>
       </c>
@@ -4742,7 +4835,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2">
       <c r="A277" t="s">
         <v>260</v>
       </c>
@@ -4750,7 +4843,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2">
       <c r="A278" t="s">
         <v>261</v>
       </c>
@@ -4758,7 +4851,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2">
       <c r="A279" t="s">
         <v>262</v>
       </c>
@@ -4766,7 +4859,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2">
       <c r="A280" t="s">
         <v>262</v>
       </c>
@@ -4774,7 +4867,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2">
       <c r="A281" t="s">
         <v>262</v>
       </c>
@@ -4782,7 +4875,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2">
       <c r="A282" t="s">
         <v>262</v>
       </c>
@@ -4790,7 +4883,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2">
       <c r="A283" t="s">
         <v>262</v>
       </c>
@@ -4798,7 +4891,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2">
       <c r="A284" t="s">
         <v>263</v>
       </c>
@@ -4806,7 +4899,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2">
       <c r="A285" t="s">
         <v>263</v>
       </c>
@@ -4814,7 +4907,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2">
       <c r="A286" t="s">
         <v>264</v>
       </c>
@@ -4822,7 +4915,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2">
       <c r="A287" t="s">
         <v>265</v>
       </c>
@@ -4830,7 +4923,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2">
       <c r="A288" t="s">
         <v>266</v>
       </c>
@@ -4838,7 +4931,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2">
       <c r="A289" t="s">
         <v>267</v>
       </c>
@@ -4846,7 +4939,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2">
       <c r="A290" t="s">
         <v>268</v>
       </c>
@@ -4854,7 +4947,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2">
       <c r="A291" t="s">
         <v>269</v>
       </c>
@@ -4862,7 +4955,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2">
       <c r="A292" t="s">
         <v>270</v>
       </c>
@@ -4870,7 +4963,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2">
       <c r="A293" t="s">
         <v>271</v>
       </c>
@@ -4878,7 +4971,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2">
       <c r="A294" t="s">
         <v>272</v>
       </c>
@@ -4886,7 +4979,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2">
       <c r="A295" t="s">
         <v>273</v>
       </c>
@@ -4894,7 +4987,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2">
       <c r="A296" t="s">
         <v>274</v>
       </c>
@@ -4902,7 +4995,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2">
       <c r="A297" t="s">
         <v>275</v>
       </c>
@@ -4910,7 +5003,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2">
       <c r="A298" t="s">
         <v>276</v>
       </c>
@@ -4918,7 +5011,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2">
       <c r="A299" t="s">
         <v>277</v>
       </c>
@@ -4926,7 +5019,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2">
       <c r="A300" t="s">
         <v>278</v>
       </c>
@@ -4934,7 +5027,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2">
       <c r="A301" t="s">
         <v>279</v>
       </c>
@@ -4942,7 +5035,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2">
       <c r="A302" t="s">
         <v>280</v>
       </c>
@@ -4950,7 +5043,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2">
       <c r="A303" t="s">
         <v>281</v>
       </c>
@@ -4958,7 +5051,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2">
       <c r="A304" t="s">
         <v>282</v>
       </c>
@@ -4966,7 +5059,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3">
       <c r="A305" t="s">
         <v>283</v>
       </c>
@@ -4974,7 +5067,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3">
       <c r="A306" t="s">
         <v>284</v>
       </c>
@@ -4982,7 +5075,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3">
       <c r="A307" t="s">
         <v>285</v>
       </c>
@@ -4990,7 +5083,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3">
       <c r="A308" t="s">
         <v>286</v>
       </c>
@@ -4998,7 +5091,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3">
       <c r="A309" t="s">
         <v>287</v>
       </c>
@@ -5006,7 +5099,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3">
       <c r="A310" t="s">
         <v>288</v>
       </c>
@@ -5014,7 +5107,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3">
       <c r="A311" t="s">
         <v>288</v>
       </c>
@@ -5022,7 +5115,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3">
       <c r="A312" t="s">
         <v>289</v>
       </c>
@@ -5030,7 +5123,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3">
       <c r="A313" t="s">
         <v>290</v>
       </c>
@@ -5038,7 +5131,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3">
       <c r="A314" t="s">
         <v>291</v>
       </c>
@@ -5046,7 +5139,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3">
       <c r="A315" t="s">
         <v>292</v>
       </c>
@@ -5054,7 +5147,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3">
       <c r="A316" t="s">
         <v>293</v>
       </c>
@@ -5062,7 +5155,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3">
       <c r="A317" t="s">
         <v>294</v>
       </c>
@@ -5070,7 +5163,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3">
       <c r="A318" t="s">
         <v>295</v>
       </c>
@@ -5078,7 +5171,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3">
       <c r="A319" t="s">
         <v>296</v>
       </c>
@@ -5086,7 +5179,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3">
       <c r="A320" t="s">
         <v>297</v>
       </c>
@@ -5097,7 +5190,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2">
       <c r="A321" t="s">
         <v>298</v>
       </c>
@@ -5105,7 +5198,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2">
       <c r="A322" t="s">
         <v>299</v>
       </c>
@@ -5113,7 +5206,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2">
       <c r="A323" t="s">
         <v>300</v>
       </c>
@@ -5121,7 +5214,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2">
       <c r="A324" t="s">
         <v>301</v>
       </c>
@@ -5129,7 +5222,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2">
       <c r="A325" t="s">
         <v>302</v>
       </c>
@@ -5137,7 +5230,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2">
       <c r="A326" t="s">
         <v>303</v>
       </c>
@@ -5145,7 +5238,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2">
       <c r="A327" t="s">
         <v>304</v>
       </c>
@@ -5153,7 +5246,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2">
       <c r="A328" t="s">
         <v>305</v>
       </c>
@@ -5161,7 +5254,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2">
       <c r="A329" t="s">
         <v>306</v>
       </c>
@@ -5169,7 +5262,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2">
       <c r="A330" t="s">
         <v>307</v>
       </c>
@@ -5177,7 +5270,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2">
       <c r="A331" t="s">
         <v>308</v>
       </c>
@@ -5185,7 +5278,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2">
       <c r="A332" t="s">
         <v>309</v>
       </c>
@@ -5193,7 +5286,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2">
       <c r="A333" t="s">
         <v>310</v>
       </c>
@@ -5201,7 +5294,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2">
       <c r="A334" t="s">
         <v>311</v>
       </c>
@@ -5209,7 +5302,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2">
       <c r="A335" t="s">
         <v>312</v>
       </c>
@@ -5217,7 +5310,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2">
       <c r="A336" t="s">
         <v>313</v>
       </c>
@@ -5225,7 +5318,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2">
       <c r="A337" t="s">
         <v>314</v>
       </c>
@@ -5233,7 +5326,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2">
       <c r="A338" t="s">
         <v>315</v>
       </c>
@@ -5241,7 +5334,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2">
       <c r="A339" t="s">
         <v>316</v>
       </c>
@@ -5249,7 +5342,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2">
       <c r="A340" t="s">
         <v>317</v>
       </c>
@@ -5257,7 +5350,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2">
       <c r="A341" t="s">
         <v>318</v>
       </c>
@@ -5265,7 +5358,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2">
       <c r="A342" t="s">
         <v>319</v>
       </c>
@@ -5273,7 +5366,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2">
       <c r="A343" t="s">
         <v>320</v>
       </c>
@@ -5281,7 +5374,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2">
       <c r="A344" t="s">
         <v>321</v>
       </c>
@@ -5289,7 +5382,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2">
       <c r="A345" t="s">
         <v>322</v>
       </c>
@@ -5297,7 +5390,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2">
       <c r="A346" t="s">
         <v>323</v>
       </c>
@@ -5305,7 +5398,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2">
       <c r="A347" t="s">
         <v>324</v>
       </c>
@@ -5313,7 +5406,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2">
       <c r="A348" t="s">
         <v>325</v>
       </c>
@@ -5321,7 +5414,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2">
       <c r="A349" t="s">
         <v>326</v>
       </c>
@@ -5329,7 +5422,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2">
       <c r="A350" t="s">
         <v>327</v>
       </c>
@@ -5337,7 +5430,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2">
       <c r="A351" t="s">
         <v>328</v>
       </c>
@@ -5345,7 +5438,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2">
       <c r="A352" t="s">
         <v>329</v>
       </c>
@@ -5353,7 +5446,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3">
       <c r="A353" t="s">
         <v>330</v>
       </c>
@@ -5364,7 +5457,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3">
       <c r="A354" t="s">
         <v>331</v>
       </c>
@@ -5375,7 +5468,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3">
       <c r="A355" t="s">
         <v>332</v>
       </c>
@@ -5383,7 +5476,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3">
       <c r="A356" t="s">
         <v>333</v>
       </c>
@@ -5391,7 +5484,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3">
       <c r="A357" t="s">
         <v>334</v>
       </c>
@@ -5399,7 +5492,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3">
       <c r="A358" t="s">
         <v>335</v>
       </c>
@@ -5407,7 +5500,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3">
       <c r="A359" t="s">
         <v>336</v>
       </c>
@@ -5415,7 +5508,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3">
       <c r="A360" t="s">
         <v>337</v>
       </c>
@@ -5423,7 +5516,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3">
       <c r="A361" t="s">
         <v>338</v>
       </c>
@@ -5431,7 +5524,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3">
       <c r="A362">
         <v>1984</v>
       </c>
@@ -5442,7 +5535,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3">
       <c r="A363" t="s">
         <v>339</v>
       </c>
@@ -5450,7 +5543,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3">
       <c r="A364" t="s">
         <v>340</v>
       </c>
@@ -5458,7 +5551,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3">
       <c r="A365" t="s">
         <v>341</v>
       </c>
@@ -5466,7 +5559,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3">
       <c r="A366" t="s">
         <v>342</v>
       </c>
@@ -5474,7 +5567,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3">
       <c r="A367" t="s">
         <v>343</v>
       </c>
@@ -5482,7 +5575,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3">
       <c r="A368" t="s">
         <v>344</v>
       </c>
@@ -5490,7 +5583,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2">
       <c r="A369" t="s">
         <v>345</v>
       </c>
@@ -5498,7 +5591,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2">
       <c r="A370" t="s">
         <v>345</v>
       </c>
@@ -5506,7 +5599,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2">
       <c r="A371" t="s">
         <v>345</v>
       </c>
@@ -5514,7 +5607,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2">
       <c r="A372" t="s">
         <v>345</v>
       </c>
@@ -5522,7 +5615,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2">
       <c r="A373" t="s">
         <v>345</v>
       </c>
@@ -5530,7 +5623,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2">
       <c r="A374" t="s">
         <v>346</v>
       </c>

--- a/livros.xlsx
+++ b/livros.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="623">
   <si>
     <t>livros</t>
   </si>
@@ -3589,6 +3589,9 @@
       <c r="B123" t="s">
         <v>442</v>
       </c>
+      <c r="C123" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
@@ -3597,6 +3600,9 @@
       <c r="B124" t="s">
         <v>443</v>
       </c>
+      <c r="C124" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
@@ -3605,6 +3611,9 @@
       <c r="B125" t="s">
         <v>444</v>
       </c>
+      <c r="C125" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
@@ -3613,6 +3622,9 @@
       <c r="B126" t="s">
         <v>445</v>
       </c>
+      <c r="C126" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
@@ -3621,6 +3633,9 @@
       <c r="B127" t="s">
         <v>353</v>
       </c>
+      <c r="C127" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
@@ -3629,6 +3644,9 @@
       <c r="B128" t="s">
         <v>446</v>
       </c>
+      <c r="C128" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
@@ -3637,6 +3655,9 @@
       <c r="B129" t="s">
         <v>447</v>
       </c>
+      <c r="C129" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
@@ -3645,6 +3666,9 @@
       <c r="B130" t="s">
         <v>448</v>
       </c>
+      <c r="C130" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
@@ -3664,6 +3688,9 @@
       <c r="B132" t="s">
         <v>449</v>
       </c>
+      <c r="C132" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
@@ -3672,6 +3699,9 @@
       <c r="B133" t="s">
         <v>450</v>
       </c>
+      <c r="C133" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
@@ -3680,6 +3710,9 @@
       <c r="B134" t="s">
         <v>451</v>
       </c>
+      <c r="C134" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
@@ -3688,6 +3721,9 @@
       <c r="B135" t="s">
         <v>353</v>
       </c>
+      <c r="C135" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
@@ -3696,6 +3732,9 @@
       <c r="B136" t="s">
         <v>452</v>
       </c>
+      <c r="C136" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
@@ -3704,6 +3743,9 @@
       <c r="B137" t="s">
         <v>453</v>
       </c>
+      <c r="C137" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
@@ -3712,6 +3754,9 @@
       <c r="B138" t="s">
         <v>454</v>
       </c>
+      <c r="C138" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
@@ -3720,6 +3765,9 @@
       <c r="B139" t="s">
         <v>455</v>
       </c>
+      <c r="C139" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
@@ -3728,6 +3776,9 @@
       <c r="B140" t="s">
         <v>456</v>
       </c>
+      <c r="C140" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
@@ -3736,6 +3787,9 @@
       <c r="B141" t="s">
         <v>457</v>
       </c>
+      <c r="C141" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
@@ -3744,6 +3798,9 @@
       <c r="B142" t="s">
         <v>458</v>
       </c>
+      <c r="C142" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
@@ -3763,6 +3820,9 @@
       <c r="B144" t="s">
         <v>460</v>
       </c>
+      <c r="C144" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
@@ -3771,6 +3831,9 @@
       <c r="B145" t="s">
         <v>461</v>
       </c>
+      <c r="C145" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
@@ -3779,6 +3842,9 @@
       <c r="B146" t="s">
         <v>462</v>
       </c>
+      <c r="C146" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
@@ -3787,6 +3853,9 @@
       <c r="B147" t="s">
         <v>463</v>
       </c>
+      <c r="C147" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
@@ -3795,6 +3864,9 @@
       <c r="B148" t="s">
         <v>464</v>
       </c>
+      <c r="C148" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
@@ -3811,6 +3883,9 @@
       <c r="A150" t="s">
         <v>144</v>
       </c>
+      <c r="C150" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
@@ -3819,6 +3894,9 @@
       <c r="B151" t="s">
         <v>466</v>
       </c>
+      <c r="C151" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
@@ -3827,6 +3905,9 @@
       <c r="B152" t="s">
         <v>467</v>
       </c>
+      <c r="C152" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
@@ -3835,6 +3916,9 @@
       <c r="B153" t="s">
         <v>468</v>
       </c>
+      <c r="C153" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
@@ -3843,6 +3927,9 @@
       <c r="B154" t="s">
         <v>469</v>
       </c>
+      <c r="C154" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
@@ -3851,6 +3938,9 @@
       <c r="B155" t="s">
         <v>470</v>
       </c>
+      <c r="C155" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
@@ -3859,6 +3949,9 @@
       <c r="B156" t="s">
         <v>471</v>
       </c>
+      <c r="C156" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
@@ -3867,6 +3960,9 @@
       <c r="B157" t="s">
         <v>472</v>
       </c>
+      <c r="C157" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
@@ -3886,6 +3982,9 @@
       <c r="B159" t="s">
         <v>474</v>
       </c>
+      <c r="C159" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
@@ -3894,11 +3993,17 @@
       <c r="B160" t="s">
         <v>475</v>
       </c>
+      <c r="C160" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
         <v>155</v>
       </c>
+      <c r="C161" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
@@ -3907,6 +4012,9 @@
       <c r="B162" t="s">
         <v>476</v>
       </c>
+      <c r="C162" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
@@ -3915,16 +4023,25 @@
       <c r="B163" t="s">
         <v>477</v>
       </c>
+      <c r="C163" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
         <v>158</v>
       </c>
+      <c r="C164" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
         <v>159</v>
       </c>
+      <c r="C165" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
@@ -3933,6 +4050,9 @@
       <c r="B166" t="s">
         <v>478</v>
       </c>
+      <c r="C166" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
@@ -3941,6 +4061,9 @@
       <c r="B167" t="s">
         <v>357</v>
       </c>
+      <c r="C167" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
@@ -3949,6 +4072,9 @@
       <c r="B168" t="s">
         <v>479</v>
       </c>
+      <c r="C168" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
@@ -3965,6 +4091,9 @@
       <c r="B170" t="s">
         <v>480</v>
       </c>
+      <c r="C170" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
@@ -3973,6 +4102,9 @@
       <c r="B171" t="s">
         <v>481</v>
       </c>
+      <c r="C171" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
@@ -3981,6 +4113,9 @@
       <c r="B172" t="s">
         <v>482</v>
       </c>
+      <c r="C172" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
@@ -3989,11 +4124,17 @@
       <c r="B173" t="s">
         <v>483</v>
       </c>
+      <c r="C173" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
         <v>168</v>
       </c>
+      <c r="C174" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
@@ -4002,6 +4143,9 @@
       <c r="B175" t="s">
         <v>484</v>
       </c>
+      <c r="C175" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
@@ -4010,133 +4154,184 @@
       <c r="B176" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="177" spans="1:2">
+      <c r="C176" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
       <c r="A177" t="s">
         <v>171</v>
       </c>
       <c r="B177" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="178" spans="1:2">
+      <c r="C177" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
       <c r="A178" t="s">
         <v>172</v>
       </c>
       <c r="B178" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="179" spans="1:2">
+      <c r="C178" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
       <c r="A179" t="s">
         <v>173</v>
       </c>
       <c r="B179" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="180" spans="1:2">
+      <c r="C179" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
       <c r="A180" t="s">
         <v>145</v>
       </c>
       <c r="B180" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="181" spans="1:2">
+      <c r="C180" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
       <c r="A181" t="s">
         <v>174</v>
       </c>
       <c r="B181" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="182" spans="1:2">
+      <c r="C181" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
       <c r="A182" t="s">
         <v>175</v>
       </c>
       <c r="B182" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="183" spans="1:2">
+      <c r="C182" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
       <c r="A183" t="s">
         <v>176</v>
       </c>
       <c r="B183" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="184" spans="1:2">
+      <c r="C183" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
       <c r="A184" t="s">
         <v>177</v>
       </c>
       <c r="B184" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="185" spans="1:2">
+      <c r="C184" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
       <c r="A185" t="s">
         <v>178</v>
       </c>
       <c r="B185" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="186" spans="1:2">
+      <c r="C185" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
       <c r="A186" t="s">
         <v>179</v>
       </c>
       <c r="B186" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="187" spans="1:2">
+      <c r="C186" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
       <c r="A187" t="s">
         <v>180</v>
       </c>
       <c r="B187" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="188" spans="1:2">
+      <c r="C187" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
       <c r="A188" t="s">
         <v>181</v>
       </c>
       <c r="B188" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="189" spans="1:2">
+      <c r="C188" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
       <c r="A189" t="s">
         <v>182</v>
       </c>
       <c r="B189" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="190" spans="1:2">
+      <c r="C189" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
       <c r="A190" t="s">
         <v>183</v>
       </c>
       <c r="B190" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="191" spans="1:2">
+      <c r="C190" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
       <c r="A191" t="s">
         <v>184</v>
       </c>
       <c r="B191" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="192" spans="1:2">
+      <c r="C191" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
       <c r="A192" t="s">
         <v>185</v>
       </c>
       <c r="B192" t="s">
         <v>496</v>
+      </c>
+      <c r="C192" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -4146,6 +4341,9 @@
       <c r="B193" t="s">
         <v>497</v>
       </c>
+      <c r="C193" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
@@ -4154,6 +4352,9 @@
       <c r="B194" t="s">
         <v>489</v>
       </c>
+      <c r="C194" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
@@ -4162,6 +4363,9 @@
       <c r="B195" t="s">
         <v>498</v>
       </c>
+      <c r="C195" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
@@ -4170,6 +4374,9 @@
       <c r="B196" t="s">
         <v>499</v>
       </c>
+      <c r="C196" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
@@ -4178,6 +4385,9 @@
       <c r="B197" t="s">
         <v>500</v>
       </c>
+      <c r="C197" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
@@ -4186,6 +4396,9 @@
       <c r="B198" t="s">
         <v>501</v>
       </c>
+      <c r="C198" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
@@ -4194,6 +4407,9 @@
       <c r="B199" t="s">
         <v>495</v>
       </c>
+      <c r="C199" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
@@ -4202,6 +4418,9 @@
       <c r="B200" t="s">
         <v>502</v>
       </c>
+      <c r="C200" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
@@ -4210,6 +4429,9 @@
       <c r="B201" t="s">
         <v>503</v>
       </c>
+      <c r="C201" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
@@ -4218,6 +4440,9 @@
       <c r="B202" t="s">
         <v>504</v>
       </c>
+      <c r="C202" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
@@ -4237,6 +4462,9 @@
       <c r="B204" t="s">
         <v>506</v>
       </c>
+      <c r="C204" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
@@ -4245,6 +4473,9 @@
       <c r="B205" t="s">
         <v>507</v>
       </c>
+      <c r="C205" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
@@ -4253,6 +4484,9 @@
       <c r="B206" t="s">
         <v>508</v>
       </c>
+      <c r="C206" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
@@ -4260,6 +4494,9 @@
       </c>
       <c r="B207" t="s">
         <v>509</v>
+      </c>
+      <c r="C207" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="208" spans="1:3">

--- a/livros.xlsx
+++ b/livros.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Helmer\Documents\py\templates automação\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DB0405-7203-4000-9FD6-523F681E7228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controle" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="621">
   <si>
     <t>livros</t>
   </si>
@@ -739,9 +745,6 @@
     <t>Feng Shui</t>
   </si>
   <si>
-    <t>O Segredo de Luísa</t>
-  </si>
-  <si>
     <t>Qualidade Ambiental: ISO 14000</t>
   </si>
   <si>
@@ -1663,9 +1666,6 @@
     <t>Rosana Braga</t>
   </si>
   <si>
-    <t>Fernando Dolabela</t>
-  </si>
-  <si>
     <t>Cyro Eyer do Valle</t>
   </si>
   <si>
@@ -1882,14 +1882,14 @@
     <t>ADITBrasil</t>
   </si>
   <si>
-    <t>Sim</t>
+    <t>NAN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1952,13 +1952,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1996,7 +2004,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2030,6 +2038,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2064,9 +2073,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2239,11 +2249,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C374"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C347"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2254,3618 +2264,3810 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C5" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C6" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C7" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C8" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C9" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C10" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C11" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C12" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C13" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C14" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C15" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C17" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C18" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C19" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C20" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C21" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C22" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C23" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C24" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C25" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C26" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C27" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C28" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C29" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C30" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C31" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C32" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C33" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C34" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
       <c r="B35" t="s">
+        <v>375</v>
+      </c>
+      <c r="C35" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>356</v>
+      </c>
+      <c r="C36" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
         <v>376</v>
       </c>
-      <c r="C35" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" t="s">
-        <v>366</v>
-      </c>
-      <c r="C36" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>357</v>
-      </c>
       <c r="C37" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
         <v>377</v>
       </c>
       <c r="C38" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
         <v>378</v>
       </c>
       <c r="C39" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
         <v>379</v>
       </c>
       <c r="C40" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
         <v>380</v>
       </c>
       <c r="C41" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
         <v>381</v>
       </c>
       <c r="C42" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
+        <v>356</v>
+      </c>
+      <c r="C43" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>356</v>
+      </c>
+      <c r="C44" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
         <v>382</v>
       </c>
-      <c r="C43" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>357</v>
-      </c>
-      <c r="C44" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>357</v>
-      </c>
       <c r="C45" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
         <v>383</v>
       </c>
       <c r="C46" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
         <v>384</v>
       </c>
       <c r="C47" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
         <v>385</v>
       </c>
       <c r="C48" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
         <v>386</v>
       </c>
       <c r="C49" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
+        <v>357</v>
+      </c>
+      <c r="C50" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" t="s">
         <v>387</v>
       </c>
-      <c r="C50" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>358</v>
-      </c>
       <c r="C51" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
+        <v>356</v>
+      </c>
+      <c r="C52" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
         <v>388</v>
       </c>
-      <c r="C52" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>357</v>
-      </c>
       <c r="C53" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
         <v>389</v>
       </c>
       <c r="C54" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" t="s">
         <v>390</v>
       </c>
       <c r="C55" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
         <v>391</v>
       </c>
       <c r="C56" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="C57" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
+        <v>380</v>
+      </c>
+      <c r="C58" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
         <v>392</v>
       </c>
-      <c r="C58" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" t="s">
-        <v>381</v>
-      </c>
       <c r="C59" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C60" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C61" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C62" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C63" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C64" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C65" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C66" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C67" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C68" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C69" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C70" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C71" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C72" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C73" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C74" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C75" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C76" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C77" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>410</v>
+        <v>346</v>
       </c>
       <c r="C78" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B79" t="s">
         <v>411</v>
       </c>
       <c r="C79" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="C80" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C81" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C82" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C83" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>415</v>
+        <v>352</v>
       </c>
       <c r="C84" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
         <v>416</v>
       </c>
       <c r="C85" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>353</v>
+        <v>417</v>
       </c>
       <c r="C86" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C87" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>418</v>
+        <v>356</v>
       </c>
       <c r="C88" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B89" t="s">
         <v>419</v>
       </c>
       <c r="C89" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C90" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B91" t="s">
         <v>420</v>
       </c>
       <c r="C91" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C92" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
         <v>421</v>
       </c>
       <c r="C93" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B94" t="s">
+        <v>422</v>
+      </c>
+      <c r="C94" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>423</v>
+      </c>
+      <c r="C95" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" t="s">
+        <v>424</v>
+      </c>
+      <c r="C96" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" t="s">
+        <v>356</v>
+      </c>
+      <c r="C97" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>356</v>
+      </c>
+      <c r="C98" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" t="s">
+        <v>356</v>
+      </c>
+      <c r="C99" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>68</v>
+      </c>
+      <c r="B101" t="s">
+        <v>425</v>
+      </c>
+      <c r="C101" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>426</v>
+      </c>
+      <c r="C102" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>427</v>
+      </c>
+      <c r="C103" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>428</v>
+      </c>
+      <c r="C104" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>429</v>
+      </c>
+      <c r="C105" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>430</v>
+      </c>
+      <c r="C106" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
         <v>357</v>
       </c>
-      <c r="C94" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" t="s">
-        <v>93</v>
-      </c>
-      <c r="B95" t="s">
-        <v>422</v>
-      </c>
-      <c r="C95" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" t="s">
-        <v>94</v>
-      </c>
-      <c r="B96" t="s">
-        <v>423</v>
-      </c>
-      <c r="C96" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" t="s">
-        <v>95</v>
-      </c>
-      <c r="B97" t="s">
-        <v>424</v>
-      </c>
-      <c r="C97" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" t="s">
-        <v>96</v>
-      </c>
-      <c r="B98" t="s">
-        <v>425</v>
-      </c>
-      <c r="C98" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" t="s">
-        <v>97</v>
-      </c>
-      <c r="B99" t="s">
-        <v>357</v>
-      </c>
-      <c r="C99" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" t="s">
-        <v>79</v>
-      </c>
-      <c r="B100" t="s">
-        <v>412</v>
-      </c>
-      <c r="C100" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" t="s">
-        <v>98</v>
-      </c>
-      <c r="B101" t="s">
-        <v>357</v>
-      </c>
-      <c r="C101" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" t="s">
-        <v>99</v>
-      </c>
-      <c r="B102" t="s">
-        <v>357</v>
-      </c>
-      <c r="C102" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" t="s">
-        <v>100</v>
-      </c>
-      <c r="C103" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" t="s">
-        <v>68</v>
-      </c>
-      <c r="B104" t="s">
-        <v>426</v>
-      </c>
-      <c r="C104" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" t="s">
-        <v>101</v>
-      </c>
-      <c r="B105" t="s">
-        <v>427</v>
-      </c>
-      <c r="C105" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" t="s">
-        <v>102</v>
-      </c>
-      <c r="B106" t="s">
-        <v>428</v>
-      </c>
-      <c r="C106" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" t="s">
-        <v>103</v>
-      </c>
-      <c r="B107" t="s">
-        <v>429</v>
-      </c>
       <c r="C107" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>378</v>
+        <v>431</v>
       </c>
       <c r="C108" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C109" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C110" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>358</v>
+        <v>433</v>
       </c>
       <c r="C111" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C112" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C113" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C114" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C115" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C116" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C117" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C118" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C119" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C120" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C121" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C122" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>442</v>
+        <v>352</v>
       </c>
       <c r="C123" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C124" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C125" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C126" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>353</v>
+        <v>448</v>
       </c>
       <c r="C127" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B128" t="s">
+        <v>449</v>
+      </c>
+      <c r="C128" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>450</v>
+      </c>
+      <c r="C129" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>352</v>
+      </c>
+      <c r="C130" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>451</v>
+      </c>
+      <c r="C131" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>452</v>
+      </c>
+      <c r="C132" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>453</v>
+      </c>
+      <c r="C133" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>454</v>
+      </c>
+      <c r="C134" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>455</v>
+      </c>
+      <c r="C135" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>456</v>
+      </c>
+      <c r="C136" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>457</v>
+      </c>
+      <c r="C137" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>458</v>
+      </c>
+      <c r="C138" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>459</v>
+      </c>
+      <c r="C139" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>460</v>
+      </c>
+      <c r="C140" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>461</v>
+      </c>
+      <c r="C141" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>462</v>
+      </c>
+      <c r="C142" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>463</v>
+      </c>
+      <c r="C143" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>464</v>
+      </c>
+      <c r="C144" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>465</v>
+      </c>
+      <c r="C146" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>466</v>
+      </c>
+      <c r="C147" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>467</v>
+      </c>
+      <c r="C148" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>468</v>
+      </c>
+      <c r="C149" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>469</v>
+      </c>
+      <c r="C150" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>470</v>
+      </c>
+      <c r="C151" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>471</v>
+      </c>
+      <c r="C152" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>472</v>
+      </c>
+      <c r="C153" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>473</v>
+      </c>
+      <c r="C154" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>474</v>
+      </c>
+      <c r="C155" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>475</v>
+      </c>
+      <c r="C157" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>476</v>
+      </c>
+      <c r="C158" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+      <c r="C160" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>477</v>
+      </c>
+      <c r="C161" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>356</v>
+      </c>
+      <c r="C162" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>478</v>
+      </c>
+      <c r="C163" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+      <c r="C164" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>479</v>
+      </c>
+      <c r="C165" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>480</v>
+      </c>
+      <c r="C166" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>481</v>
+      </c>
+      <c r="C167" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>482</v>
+      </c>
+      <c r="C168" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>483</v>
+      </c>
+      <c r="C170" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>484</v>
+      </c>
+      <c r="C171" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>485</v>
+      </c>
+      <c r="C172" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>356</v>
+      </c>
+      <c r="C173" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>352</v>
+      </c>
+      <c r="C174" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
         <v>446</v>
       </c>
-      <c r="C128" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" t="s">
-        <v>124</v>
-      </c>
-      <c r="B129" t="s">
-        <v>447</v>
-      </c>
-      <c r="C129" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" t="s">
-        <v>125</v>
-      </c>
-      <c r="B130" t="s">
-        <v>448</v>
-      </c>
-      <c r="C130" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" t="s">
-        <v>97</v>
-      </c>
-      <c r="B131" t="s">
-        <v>357</v>
-      </c>
-      <c r="C131" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" t="s">
-        <v>126</v>
-      </c>
-      <c r="B132" t="s">
-        <v>449</v>
-      </c>
-      <c r="C132" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" t="s">
-        <v>127</v>
-      </c>
-      <c r="B133" t="s">
-        <v>450</v>
-      </c>
-      <c r="C133" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" t="s">
-        <v>128</v>
-      </c>
-      <c r="B134" t="s">
-        <v>451</v>
-      </c>
-      <c r="C134" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" t="s">
-        <v>129</v>
-      </c>
-      <c r="B135" t="s">
-        <v>353</v>
-      </c>
-      <c r="C135" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" t="s">
-        <v>130</v>
-      </c>
-      <c r="B136" t="s">
-        <v>452</v>
-      </c>
-      <c r="C136" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" t="s">
-        <v>131</v>
-      </c>
-      <c r="B137" t="s">
-        <v>453</v>
-      </c>
-      <c r="C137" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" t="s">
-        <v>132</v>
-      </c>
-      <c r="B138" t="s">
-        <v>454</v>
-      </c>
-      <c r="C138" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" t="s">
-        <v>133</v>
-      </c>
-      <c r="B139" t="s">
-        <v>455</v>
-      </c>
-      <c r="C139" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" t="s">
-        <v>134</v>
-      </c>
-      <c r="B140" t="s">
-        <v>456</v>
-      </c>
-      <c r="C140" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" t="s">
-        <v>135</v>
-      </c>
-      <c r="B141" t="s">
-        <v>457</v>
-      </c>
-      <c r="C141" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" t="s">
-        <v>136</v>
-      </c>
-      <c r="B142" t="s">
-        <v>458</v>
-      </c>
-      <c r="C142" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" t="s">
-        <v>137</v>
-      </c>
-      <c r="B143" t="s">
-        <v>459</v>
-      </c>
-      <c r="C143" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" t="s">
-        <v>138</v>
-      </c>
-      <c r="B144" t="s">
-        <v>460</v>
-      </c>
-      <c r="C144" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" t="s">
-        <v>139</v>
-      </c>
-      <c r="B145" t="s">
-        <v>461</v>
-      </c>
-      <c r="C145" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" t="s">
-        <v>140</v>
-      </c>
-      <c r="B146" t="s">
-        <v>462</v>
-      </c>
-      <c r="C146" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" t="s">
-        <v>141</v>
-      </c>
-      <c r="B147" t="s">
-        <v>463</v>
-      </c>
-      <c r="C147" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" t="s">
-        <v>142</v>
-      </c>
-      <c r="B148" t="s">
-        <v>464</v>
-      </c>
-      <c r="C148" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" t="s">
-        <v>143</v>
-      </c>
-      <c r="B149" t="s">
-        <v>465</v>
-      </c>
-      <c r="C149" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" t="s">
-        <v>144</v>
-      </c>
-      <c r="C150" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
-        <v>145</v>
-      </c>
-      <c r="B151" t="s">
-        <v>466</v>
-      </c>
-      <c r="C151" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" t="s">
-        <v>146</v>
-      </c>
-      <c r="B152" t="s">
-        <v>467</v>
-      </c>
-      <c r="C152" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" t="s">
-        <v>147</v>
-      </c>
-      <c r="B153" t="s">
-        <v>468</v>
-      </c>
-      <c r="C153" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" t="s">
-        <v>148</v>
-      </c>
-      <c r="B154" t="s">
-        <v>469</v>
-      </c>
-      <c r="C154" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" t="s">
-        <v>149</v>
-      </c>
-      <c r="B155" t="s">
-        <v>470</v>
-      </c>
-      <c r="C155" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" t="s">
-        <v>150</v>
-      </c>
-      <c r="B156" t="s">
-        <v>471</v>
-      </c>
-      <c r="C156" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" t="s">
-        <v>151</v>
-      </c>
-      <c r="B157" t="s">
-        <v>472</v>
-      </c>
-      <c r="C157" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" t="s">
-        <v>152</v>
-      </c>
-      <c r="B158" t="s">
-        <v>473</v>
-      </c>
-      <c r="C158" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" t="s">
-        <v>153</v>
-      </c>
-      <c r="B159" t="s">
-        <v>474</v>
-      </c>
-      <c r="C159" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" t="s">
-        <v>154</v>
-      </c>
-      <c r="B160" t="s">
-        <v>475</v>
-      </c>
-      <c r="C160" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" t="s">
-        <v>155</v>
-      </c>
-      <c r="C161" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" t="s">
-        <v>156</v>
-      </c>
-      <c r="B162" t="s">
-        <v>476</v>
-      </c>
-      <c r="C162" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163" t="s">
-        <v>157</v>
-      </c>
-      <c r="B163" t="s">
-        <v>477</v>
-      </c>
-      <c r="C163" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" t="s">
-        <v>158</v>
-      </c>
-      <c r="C164" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" t="s">
-        <v>159</v>
-      </c>
-      <c r="C165" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" t="s">
-        <v>160</v>
-      </c>
-      <c r="B166" t="s">
-        <v>478</v>
-      </c>
-      <c r="C166" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" t="s">
-        <v>161</v>
-      </c>
-      <c r="B167" t="s">
-        <v>357</v>
-      </c>
-      <c r="C167" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" t="s">
-        <v>162</v>
-      </c>
-      <c r="B168" t="s">
-        <v>479</v>
-      </c>
-      <c r="C168" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" t="s">
-        <v>163</v>
-      </c>
-      <c r="C169" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" t="s">
-        <v>164</v>
-      </c>
-      <c r="B170" t="s">
-        <v>480</v>
-      </c>
-      <c r="C170" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" t="s">
-        <v>165</v>
-      </c>
-      <c r="B171" t="s">
-        <v>481</v>
-      </c>
-      <c r="C171" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" t="s">
-        <v>166</v>
-      </c>
-      <c r="B172" t="s">
-        <v>482</v>
-      </c>
-      <c r="C172" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="A173" t="s">
-        <v>167</v>
-      </c>
-      <c r="B173" t="s">
-        <v>483</v>
-      </c>
-      <c r="C173" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="A174" t="s">
-        <v>168</v>
-      </c>
-      <c r="C174" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" t="s">
-        <v>169</v>
-      </c>
-      <c r="B175" t="s">
-        <v>484</v>
-      </c>
       <c r="C175" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C176" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C177" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>357</v>
+        <v>488</v>
       </c>
       <c r="C178" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>353</v>
+        <v>489</v>
       </c>
       <c r="C179" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="C180" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>447</v>
+        <v>491</v>
       </c>
       <c r="C181" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C182" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B183" t="s">
+        <v>493</v>
+      </c>
+      <c r="C183" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>494</v>
+      </c>
+      <c r="C184" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>494</v>
+      </c>
+      <c r="C185" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>495</v>
+      </c>
+      <c r="C186" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>496</v>
+      </c>
+      <c r="C187" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
         <v>488</v>
       </c>
-      <c r="C183" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" t="s">
-        <v>177</v>
-      </c>
-      <c r="B184" t="s">
-        <v>489</v>
-      </c>
-      <c r="C184" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" t="s">
-        <v>178</v>
-      </c>
-      <c r="B185" t="s">
-        <v>490</v>
-      </c>
-      <c r="C185" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" t="s">
-        <v>179</v>
-      </c>
-      <c r="B186" t="s">
-        <v>491</v>
-      </c>
-      <c r="C186" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" t="s">
-        <v>180</v>
-      </c>
-      <c r="B187" t="s">
-        <v>492</v>
-      </c>
-      <c r="C187" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" t="s">
-        <v>181</v>
-      </c>
-      <c r="B188" t="s">
-        <v>493</v>
-      </c>
       <c r="C188" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>497</v>
+      </c>
+      <c r="C189" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>498</v>
+      </c>
+      <c r="C190" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>499</v>
+      </c>
+      <c r="C191" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>500</v>
+      </c>
+      <c r="C192" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
         <v>494</v>
       </c>
-      <c r="C189" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" t="s">
-        <v>183</v>
-      </c>
-      <c r="B190" t="s">
-        <v>495</v>
-      </c>
-      <c r="C190" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" t="s">
-        <v>184</v>
-      </c>
-      <c r="B191" t="s">
-        <v>495</v>
-      </c>
-      <c r="C191" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" t="s">
-        <v>185</v>
-      </c>
-      <c r="B192" t="s">
-        <v>496</v>
-      </c>
-      <c r="C192" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" t="s">
-        <v>186</v>
-      </c>
-      <c r="B193" t="s">
-        <v>497</v>
-      </c>
       <c r="C193" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C194" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C195" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C196" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C197" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C198" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="C199" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C200" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C201" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C202" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C203" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C204" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C205" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C206" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C207" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2">
+        <v>515</v>
+      </c>
+      <c r="C208" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2">
+        <v>516</v>
+      </c>
+      <c r="C209" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2">
+        <v>514</v>
+      </c>
+      <c r="C210" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
+        <v>517</v>
+      </c>
+      <c r="C211" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2">
+        <v>518</v>
+      </c>
+      <c r="C212" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2">
+        <v>519</v>
+      </c>
+      <c r="C213" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2">
+        <v>520</v>
+      </c>
+      <c r="C214" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
+        <v>521</v>
+      </c>
+      <c r="C215" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
+        <v>522</v>
+      </c>
+      <c r="C216" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2">
+        <v>523</v>
+      </c>
+      <c r="C217" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
+        <v>524</v>
+      </c>
+      <c r="C218" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
+        <v>525</v>
+      </c>
+      <c r="C219" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2">
+        <v>526</v>
+      </c>
+      <c r="C220" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2">
+        <v>527</v>
+      </c>
+      <c r="C221" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2">
+        <v>528</v>
+      </c>
+      <c r="C222" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
+        <v>529</v>
+      </c>
+      <c r="C223" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3">
+        <v>530</v>
+      </c>
+      <c r="C224" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
+        <v>531</v>
+      </c>
+      <c r="C225" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3">
+        <v>532</v>
+      </c>
+      <c r="C226" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3">
+        <v>533</v>
+      </c>
+      <c r="C227" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3">
+        <v>534</v>
+      </c>
+      <c r="C228" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3">
+        <v>535</v>
+      </c>
+      <c r="C229" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
+        <v>536</v>
+      </c>
+      <c r="C230" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3">
+        <v>537</v>
+      </c>
+      <c r="C231" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
+        <v>538</v>
+      </c>
+      <c r="C232" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
+        <v>539</v>
+      </c>
+      <c r="C233" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
+        <v>540</v>
+      </c>
+      <c r="C234" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
+        <v>541</v>
+      </c>
+      <c r="C235" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
+        <v>542</v>
+      </c>
+      <c r="C236" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
+        <v>543</v>
+      </c>
+      <c r="C237" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
+        <v>544</v>
+      </c>
+      <c r="C238" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C239" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2">
+        <v>546</v>
+      </c>
+      <c r="C240" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2">
+        <v>547</v>
+      </c>
+      <c r="C241" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
+        <v>548</v>
+      </c>
+      <c r="C242" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2">
+        <v>549</v>
+      </c>
+      <c r="C243" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2">
+        <v>550</v>
+      </c>
+      <c r="C244" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2">
+        <v>551</v>
+      </c>
+      <c r="C245" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2">
+        <v>552</v>
+      </c>
+      <c r="C246" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2">
+        <v>553</v>
+      </c>
+      <c r="C247" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2">
+        <v>554</v>
+      </c>
+      <c r="C248" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B249" t="s">
+        <v>555</v>
+      </c>
+      <c r="C249" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>556</v>
+      </c>
+      <c r="C250" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>557</v>
+      </c>
+      <c r="C251" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>558</v>
+      </c>
+      <c r="C252" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>559</v>
+      </c>
+      <c r="C253" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>560</v>
+      </c>
+      <c r="C254" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>561</v>
+      </c>
+      <c r="C255" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>561</v>
+      </c>
+      <c r="C256" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>562</v>
+      </c>
+      <c r="C257" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>563</v>
+      </c>
+      <c r="C258" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>564</v>
+      </c>
+      <c r="C259" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>565</v>
+      </c>
+      <c r="C260" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="250" spans="1:2">
-      <c r="A250" t="s">
-        <v>243</v>
-      </c>
-      <c r="B250" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2">
-      <c r="A251" t="s">
-        <v>244</v>
-      </c>
-      <c r="B251" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2">
-      <c r="A252" t="s">
-        <v>245</v>
-      </c>
-      <c r="B252" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2">
-      <c r="A253" t="s">
-        <v>245</v>
-      </c>
-      <c r="B253" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2">
-      <c r="A254" t="s">
-        <v>245</v>
-      </c>
-      <c r="B254" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2">
-      <c r="A255" t="s">
-        <v>245</v>
-      </c>
-      <c r="B255" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2">
-      <c r="A256" t="s">
-        <v>245</v>
-      </c>
-      <c r="B256" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3">
-      <c r="A257" t="s">
-        <v>245</v>
-      </c>
-      <c r="B257" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3">
-      <c r="A258" t="s">
-        <v>245</v>
-      </c>
-      <c r="B258" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" t="s">
-        <v>246</v>
-      </c>
-      <c r="B259" t="s">
-        <v>554</v>
-      </c>
-      <c r="C259" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3">
-      <c r="A260" t="s">
-        <v>246</v>
-      </c>
-      <c r="B260" t="s">
-        <v>554</v>
-      </c>
-      <c r="C260" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3">
-      <c r="A261" t="s">
-        <v>246</v>
-      </c>
-      <c r="B261" t="s">
-        <v>554</v>
-      </c>
       <c r="C261" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C262" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="C263" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="C264" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3">
+        <v>568</v>
+      </c>
+      <c r="C265" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3">
+        <v>568</v>
+      </c>
+      <c r="C266" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3">
+        <v>568</v>
+      </c>
+      <c r="C267" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3">
+        <v>568</v>
+      </c>
+      <c r="C268" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3">
+        <v>568</v>
+      </c>
+      <c r="C269" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3">
+        <v>568</v>
+      </c>
+      <c r="C270" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3">
+        <v>568</v>
+      </c>
+      <c r="C271" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2">
+        <v>568</v>
+      </c>
+      <c r="C272" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2">
+        <v>568</v>
+      </c>
+      <c r="C273" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B274" t="s">
+        <v>568</v>
+      </c>
+      <c r="C274" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>568</v>
+      </c>
+      <c r="C275" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>568</v>
+      </c>
+      <c r="C276" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="275" spans="1:2">
-      <c r="A275" t="s">
-        <v>258</v>
-      </c>
-      <c r="B275" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2">
-      <c r="A276" t="s">
-        <v>259</v>
-      </c>
-      <c r="B276" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2">
-      <c r="A277" t="s">
-        <v>260</v>
-      </c>
-      <c r="B277" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2">
+      <c r="C277" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2">
+        <v>564</v>
+      </c>
+      <c r="C278" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2">
+        <v>569</v>
+      </c>
+      <c r="C279" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2">
+        <v>570</v>
+      </c>
+      <c r="C280" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2">
+        <v>570</v>
+      </c>
+      <c r="C281" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2">
+        <v>570</v>
+      </c>
+      <c r="C282" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2">
+        <v>570</v>
+      </c>
+      <c r="C283" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2">
+        <v>570</v>
+      </c>
+      <c r="C284" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2">
+        <v>570</v>
+      </c>
+      <c r="C285" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="B286" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="287" spans="1:2">
+      <c r="C286" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="B287" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="288" spans="1:2">
+      <c r="C287" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="B288" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="289" spans="1:2">
+      <c r="C288" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="B289" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="290" spans="1:2">
+      <c r="C289" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="B290" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="291" spans="1:2">
+      <c r="C290" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2">
+        <v>571</v>
+      </c>
+      <c r="C291" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
+        <v>571</v>
+      </c>
+      <c r="C292" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
+        <v>571</v>
+      </c>
+      <c r="C293" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
+        <v>571</v>
+      </c>
+      <c r="C294" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2">
+        <v>571</v>
+      </c>
+      <c r="C295" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2">
+        <v>571</v>
+      </c>
+      <c r="C296" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
+        <v>572</v>
+      </c>
+      <c r="C297" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2">
+        <v>573</v>
+      </c>
+      <c r="C298" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
+        <v>543</v>
+      </c>
+      <c r="C299" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
+        <v>574</v>
+      </c>
+      <c r="C300" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2">
+        <v>575</v>
+      </c>
+      <c r="C301" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2">
+        <v>576</v>
+      </c>
+      <c r="C302" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2">
+        <v>577</v>
+      </c>
+      <c r="C303" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3">
+        <v>578</v>
+      </c>
+      <c r="C304" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3">
+        <v>579</v>
+      </c>
+      <c r="C305" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3">
+        <v>580</v>
+      </c>
+      <c r="C306" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3">
+        <v>581</v>
+      </c>
+      <c r="C307" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3">
+        <v>582</v>
+      </c>
+      <c r="C308" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3">
+        <v>583</v>
+      </c>
+      <c r="C309" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3">
+        <v>584</v>
+      </c>
+      <c r="C310" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3">
+        <v>585</v>
+      </c>
+      <c r="C311" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3">
+        <v>586</v>
+      </c>
+      <c r="C312" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3">
+        <v>587</v>
+      </c>
+      <c r="C313" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3">
+        <v>588</v>
+      </c>
+      <c r="C314" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3">
+        <v>589</v>
+      </c>
+      <c r="C315" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3">
+        <v>590</v>
+      </c>
+      <c r="C316" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3">
+        <v>591</v>
+      </c>
+      <c r="C317" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3">
+        <v>592</v>
+      </c>
+      <c r="C318" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3">
+        <v>576</v>
+      </c>
+      <c r="C319" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="C320" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
+        <v>594</v>
+      </c>
+      <c r="C321" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2">
+        <v>595</v>
+      </c>
+      <c r="C322" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="324" spans="1:2">
+        <v>596</v>
+      </c>
+      <c r="C323" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
+        <v>597</v>
+      </c>
+      <c r="C324" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
+        <v>598</v>
+      </c>
+      <c r="C325" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
+        <v>599</v>
+      </c>
+      <c r="C326" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2">
+        <v>600</v>
+      </c>
+      <c r="C327" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
+        <v>601</v>
+      </c>
+      <c r="C328" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2">
+        <v>601</v>
+      </c>
+      <c r="C329" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
+        <v>602</v>
+      </c>
+      <c r="C330" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
+        <v>603</v>
+      </c>
+      <c r="C331" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
+        <v>604</v>
+      </c>
+      <c r="C332" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2">
+        <v>605</v>
+      </c>
+      <c r="C333" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2">
+        <v>606</v>
+      </c>
+      <c r="C334" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
+        <v>607</v>
+      </c>
+      <c r="C335" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
+        <v>608</v>
+      </c>
+      <c r="C336" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2">
+        <v>609</v>
+      </c>
+      <c r="C337" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2">
-      <c r="A339" t="s">
-        <v>316</v>
+        <v>610</v>
+      </c>
+      <c r="C338" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>1984</v>
       </c>
       <c r="B339" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2">
+        <v>611</v>
+      </c>
+      <c r="C339" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2">
+        <v>612</v>
+      </c>
+      <c r="C340" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
+        <v>613</v>
+      </c>
+      <c r="C341" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
+        <v>614</v>
+      </c>
+      <c r="C342" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
+        <v>615</v>
+      </c>
+      <c r="C343" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2">
+        <v>616</v>
+      </c>
+      <c r="C344" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
+        <v>617</v>
+      </c>
+      <c r="C345" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
+        <v>618</v>
+      </c>
+      <c r="C346" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2">
-      <c r="A348" t="s">
-        <v>325</v>
-      </c>
-      <c r="B348" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2">
-      <c r="A349" t="s">
-        <v>326</v>
-      </c>
-      <c r="B349" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
-      <c r="A350" t="s">
-        <v>327</v>
-      </c>
-      <c r="B350" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2">
-      <c r="A351" t="s">
-        <v>328</v>
-      </c>
-      <c r="B351" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2">
-      <c r="A352" t="s">
-        <v>329</v>
-      </c>
-      <c r="B352" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3">
-      <c r="A353" t="s">
-        <v>330</v>
-      </c>
-      <c r="B353" t="s">
-        <v>604</v>
-      </c>
-      <c r="C353" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3">
-      <c r="A354" t="s">
-        <v>331</v>
-      </c>
-      <c r="B354" t="s">
-        <v>605</v>
-      </c>
-      <c r="C354" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3">
-      <c r="A355" t="s">
-        <v>332</v>
-      </c>
-      <c r="B355" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3">
-      <c r="A356" t="s">
-        <v>333</v>
-      </c>
-      <c r="B356" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3">
-      <c r="A357" t="s">
-        <v>334</v>
-      </c>
-      <c r="B357" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3">
-      <c r="A358" t="s">
-        <v>335</v>
-      </c>
-      <c r="B358" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3">
-      <c r="A359" t="s">
-        <v>336</v>
-      </c>
-      <c r="B359" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3">
-      <c r="A360" t="s">
-        <v>337</v>
-      </c>
-      <c r="B360" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3">
-      <c r="A361" t="s">
-        <v>338</v>
-      </c>
-      <c r="B361" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3">
-      <c r="A362">
-        <v>1984</v>
-      </c>
-      <c r="B362" t="s">
-        <v>613</v>
-      </c>
-      <c r="C362" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3">
-      <c r="A363" t="s">
-        <v>339</v>
-      </c>
-      <c r="B363" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3">
-      <c r="A364" t="s">
-        <v>340</v>
-      </c>
-      <c r="B364" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3">
-      <c r="A365" t="s">
-        <v>341</v>
-      </c>
-      <c r="B365" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3">
-      <c r="A366" t="s">
-        <v>342</v>
-      </c>
-      <c r="B366" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3">
-      <c r="A367" t="s">
-        <v>343</v>
-      </c>
-      <c r="B367" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3">
-      <c r="A368" t="s">
-        <v>344</v>
-      </c>
-      <c r="B368" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" t="s">
-        <v>345</v>
-      </c>
-      <c r="B369" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" t="s">
-        <v>345</v>
-      </c>
-      <c r="B370" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="371" spans="1:2">
-      <c r="A371" t="s">
-        <v>345</v>
-      </c>
-      <c r="B371" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2">
-      <c r="A372" t="s">
-        <v>345</v>
-      </c>
-      <c r="B372" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="373" spans="1:2">
-      <c r="A373" t="s">
-        <v>345</v>
-      </c>
-      <c r="B373" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="374" spans="1:2">
-      <c r="A374" t="s">
-        <v>346</v>
-      </c>
-      <c r="B374" t="s">
-        <v>621</v>
+      <c r="C347" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>
